--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128405220</v>
+        <v>136878592</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,26 +1074,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1107,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524167</v>
+        <v>524149</v>
       </c>
       <c r="R5" t="n">
-        <v>6714589</v>
+        <v>6714564</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,22 +1142,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,56 +1183,60 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128405220</t>
+          <t>https://artportalen.se/Sighting/136878592</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127374654</v>
+        <v>128405220</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524109</v>
+        <v>524167</v>
       </c>
       <c r="R6" t="n">
-        <v>6714794</v>
+        <v>6714589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,22 +1263,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,61 +1293,52 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127374654</t>
+          <t>https://artportalen.se/Sighting/128405220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123649906</v>
+        <v>127374654</v>
       </c>
       <c r="B7" t="n">
-        <v>104628</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1346,14 +1346,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsbo, Smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524108</v>
+        <v>524109</v>
       </c>
       <c r="R7" t="n">
-        <v>6714516</v>
+        <v>6714794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,22 +1380,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,16 +1410,142 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374654</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123649906</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524108</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6714516</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123649906</t>
         </is>
@@ -1433,6 +1559,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>136878592</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>136878592</v>
       </c>
       <c r="B5" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -1096,16 +1096,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Smedsbo, Smedsbo, Dlr</t>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>136878592</v>
       </c>
       <c r="B5" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>136878592</v>
       </c>
       <c r="B5" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>136878592</v>
       </c>
       <c r="B5" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
